--- a/output/pdf_financials_xlsx/ACAP.P.xlsx
+++ b/output/pdf_financials_xlsx/ACAP.P.xlsx
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0.048083</v>
+        <v>0.062331</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0.048083</v>
+        <v>0.062331</v>
       </c>
       <c r="D92" s="3" t="n">
         <v>0.062331</v>
@@ -3610,7 +3610,11 @@
           <t>Reserve for warrants (Note 3)</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" s="5" t="n">
         <v>0.014248</v>
       </c>

--- a/output/pdf_financials_xlsx/ACAP.P.xlsx
+++ b/output/pdf_financials_xlsx/ACAP.P.xlsx
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="B120" s="3" t="n">
-        <v>0</v>
+        <v>0.1315</v>
       </c>
       <c r="C120" s="3" t="n">
         <v>0</v>
@@ -4272,7 +4272,11 @@
           <t>Issuance of common shares, net of issuance costs</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E34" s="5" t="n">
         <v>0.1315</v>
       </c>
